--- a/12617839 (4).xlsx
+++ b/12617839 (4).xlsx
@@ -3590,10 +3590,7 @@
       <c r="F57" s="14"/>
       <c r="G57" s="14"/>
       <c r="H57" s="14"/>
-      <c r="I57" s="15">
-        <f t="shared" ref="I57:I120" si="2">IF(SUM(B41:F41,H41)=0,"",SUM(B41:F41,H41))</f>
-        <v>935</v>
-      </c>
+      <c r="I57" s="15"/>
       <c r="J57" s="15"/>
       <c r="K57" s="16"/>
       <c r="L57" s="16"/>
@@ -3609,10 +3606,7 @@
       <c r="F58" s="14"/>
       <c r="G58" s="14"/>
       <c r="H58" s="14"/>
-      <c r="I58" s="15">
-        <f t="shared" si="2"/>
-        <v>890</v>
-      </c>
+      <c r="I58" s="15"/>
       <c r="J58" s="15"/>
       <c r="K58" s="16"/>
       <c r="L58" s="16"/>
@@ -3628,10 +3622,7 @@
       <c r="F59" s="14"/>
       <c r="G59" s="14"/>
       <c r="H59" s="14"/>
-      <c r="I59" s="15">
-        <f t="shared" si="2"/>
-        <v>880</v>
-      </c>
+      <c r="I59" s="15"/>
       <c r="J59" s="15"/>
       <c r="K59" s="16"/>
       <c r="L59" s="16"/>
@@ -3647,10 +3638,7 @@
       <c r="F60" s="14"/>
       <c r="G60" s="14"/>
       <c r="H60" s="14"/>
-      <c r="I60" s="15">
-        <f t="shared" si="2"/>
-        <v>770</v>
-      </c>
+      <c r="I60" s="15"/>
       <c r="J60" s="15"/>
       <c r="K60" s="16"/>
       <c r="L60" s="16"/>
@@ -3667,7 +3655,7 @@
       <c r="G61" s="14"/>
       <c r="H61" s="14"/>
       <c r="I61" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" ref="I57:I120" si="2">IF(SUM(B45:F45,H45)=0,"",SUM(B45:F45,H45))</f>
         <v/>
       </c>
       <c r="J61" s="15"/>
@@ -3916,9 +3904,9 @@
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="J73" s="15">
+      <c r="J73" s="15" t="str">
         <f t="shared" si="3"/>
-        <v>505</v>
+        <v/>
       </c>
       <c r="K73" s="16"/>
       <c r="L73" s="16"/>
@@ -3938,9 +3926,9 @@
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="J74" s="15">
+      <c r="J74" s="15" t="str">
         <f t="shared" si="3"/>
-        <v>550</v>
+        <v/>
       </c>
       <c r="K74" s="16"/>
       <c r="L74" s="16"/>
@@ -3960,9 +3948,9 @@
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="J75" s="15">
+      <c r="J75" s="15" t="str">
         <f t="shared" si="3"/>
-        <v>560</v>
+        <v/>
       </c>
       <c r="K75" s="16"/>
       <c r="L75" s="16"/>
@@ -3982,9 +3970,9 @@
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="J76" s="15">
+      <c r="J76" s="15" t="str">
         <f t="shared" si="3"/>
-        <v>670</v>
+        <v/>
       </c>
       <c r="K76" s="16"/>
       <c r="L76" s="16"/>
